--- a/business_surveys/010_marina_scheduling_survey--business_surveys.xlsx
+++ b/business_surveys/010_marina_scheduling_survey--business_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -987,8 +987,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1016,12 +1016,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'morning'}</t>
+          <t>morning</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'morning'}</t>
+          <t>morning</t>
         </is>
       </c>
     </row>
@@ -1033,12 +1033,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'afternoon'}</t>
+          <t>afternoon</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'afternoon'}</t>
+          <t>afternoon</t>
         </is>
       </c>
     </row>
@@ -1050,12 +1050,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'evening'}</t>
+          <t>evening</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'evening'}</t>
+          <t>evening</t>
         </is>
       </c>
     </row>
@@ -1067,12 +1067,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'morning'}</t>
+          <t>morning</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'morning'}</t>
+          <t>morning</t>
         </is>
       </c>
     </row>
@@ -1084,12 +1084,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'afternoon'}</t>
+          <t>afternoon</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'afternoon'}</t>
+          <t>afternoon</t>
         </is>
       </c>
     </row>
@@ -1101,12 +1101,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'evening'}</t>
+          <t>evening</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'evening'}</t>
+          <t>evening</t>
         </is>
       </c>
     </row>
@@ -1118,12 +1118,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'monday'}</t>
+          <t>monday</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Monday'}</t>
+          <t>Monday</t>
         </is>
       </c>
     </row>
@@ -1135,12 +1135,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'tuesday'}</t>
+          <t>tuesday</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Tuesday'}</t>
+          <t>Tuesday</t>
         </is>
       </c>
     </row>
@@ -1152,12 +1152,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'wednesday'}</t>
+          <t>wednesday</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Wednesday'}</t>
+          <t>Wednesday</t>
         </is>
       </c>
     </row>
@@ -1169,12 +1169,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'thursday'}</t>
+          <t>thursday</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Thursday'}</t>
+          <t>Thursday</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'friday'}</t>
+          <t>friday</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Friday'}</t>
+          <t>Friday</t>
         </is>
       </c>
     </row>
@@ -1203,12 +1203,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_6,_'label':_'saturday'}</t>
+          <t>saturday</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 6, 'label': 'Saturday'}</t>
+          <t>Saturday</t>
         </is>
       </c>
     </row>
@@ -1220,12 +1220,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_7,_'label':_'sunday'}</t>
+          <t>sunday</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 7, 'label': 'Sunday'}</t>
+          <t>Sunday</t>
         </is>
       </c>
     </row>
@@ -1237,12 +1237,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'15_feet'}</t>
+          <t>15_feet</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': '15 feet'}</t>
+          <t>15 feet</t>
         </is>
       </c>
     </row>
@@ -1254,12 +1254,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'20_feet'}</t>
+          <t>20_feet</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': '20 feet'}</t>
+          <t>20 feet</t>
         </is>
       </c>
     </row>
@@ -1271,12 +1271,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'25_feet'}</t>
+          <t>25_feet</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': '25 feet'}</t>
+          <t>25 feet</t>
         </is>
       </c>
     </row>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'email'}</t>
+          <t>email</t>
         </is>
       </c>
     </row>
@@ -1305,12 +1305,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
     </row>
@@ -1322,12 +1322,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'text'}</t>
+          <t>text</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'text'}</t>
+          <t>text</t>
         </is>
       </c>
     </row>
@@ -1339,12 +1339,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'call'}</t>
+          <t>call</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'call'}</t>
+          <t>call</t>
         </is>
       </c>
     </row>
@@ -1356,12 +1356,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'email'}</t>
+          <t>email</t>
         </is>
       </c>
     </row>
@@ -1373,12 +1373,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'text'}</t>
+          <t>text</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'text'}</t>
+          <t>text</t>
         </is>
       </c>
     </row>
@@ -1390,12 +1390,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'sailboat'}</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'sailboat'}</t>
+          <t>sailboat</t>
         </is>
       </c>
     </row>
@@ -1407,12 +1407,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'powerboat'}</t>
+          <t>powerboat</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'powerboat'}</t>
+          <t>powerboat</t>
         </is>
       </c>
     </row>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'other'}</t>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -1441,12 +1441,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'location1'}</t>
+          <t>location1</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'location1'}</t>
+          <t>location1</t>
         </is>
       </c>
     </row>
@@ -1458,12 +1458,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'location2'}</t>
+          <t>location2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'location2'}</t>
+          <t>location2</t>
         </is>
       </c>
     </row>
@@ -1475,12 +1475,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'location3'}</t>
+          <t>location3</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'location3'}</t>
+          <t>location3</t>
         </is>
       </c>
     </row>
